--- a/output/pdf_financials_xlsx/DRC.xlsx
+++ b/output/pdf_financials_xlsx/DRC.xlsx
@@ -2211,16 +2211,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.265596</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.265596</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.430929</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>4.42095</v>
       </c>
     </row>
     <row r="93">
@@ -3632,7 +3632,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -4378,7 +4382,11 @@
           <t>Reserves 3,430,929</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
         <v>1.265596</v>
       </c>
@@ -4814,7 +4822,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n">
         <v>1.265596</v>
       </c>

--- a/output/pdf_financials_xlsx/DRC.xlsx
+++ b/output/pdf_financials_xlsx/DRC.xlsx
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.002206</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.48124</v>
+        <v>-1.483446</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-1.411087</v>
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.47352</v>
+        <v>-1.475726</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-1.403053</v>
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.241905</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.171941</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.320255</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.191599</v>
       </c>
     </row>
     <row r="35">
@@ -1115,16 +1115,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.241905</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.171941</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.320255</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.191599</v>
       </c>
     </row>
     <row r="37">
@@ -1343,16 +1343,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.457038</v>
+        <v>0.215133</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.342832</v>
+        <v>0.170891</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.370817</v>
+        <v>0.050562</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.25305</v>
+        <v>0.061451</v>
       </c>
     </row>
     <row r="49">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">

--- a/output/pdf_financials_xlsx/DRC.xlsx
+++ b/output/pdf_financials_xlsx/DRC.xlsx
@@ -2376,10 +2376,10 @@
         <v>-0.007526</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.00565</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.00475</v>
       </c>
     </row>
     <row r="102">
@@ -2471,10 +2471,10 @@
         <v>0.386455</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.243372</v>
+        <v>0.249022</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.125099</v>
+        <v>-0.129849</v>
       </c>
     </row>
     <row r="107">
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.08108799999999999</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -2566,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.104753</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.104753</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -3030,7 +3030,7 @@
         <v>-1.109272</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-2.813243</v>
+        <v>-2.917996</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-1.696469</v>
@@ -5260,7 +5260,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -5428,7 +5432,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -6106,7 +6114,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -6212,7 +6224,11 @@
           <t>Purchases of equipment</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -6248,7 +6264,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
